--- a/data/trans_bre/P14B23-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Habitat-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,8</t>
+          <t>4,91; 9,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,65</t>
+          <t>4,19; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,99</t>
+          <t>-1,61; 3,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167,99; 769,75</t>
+          <t>166,6; 743,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>130,64; 779,81</t>
+          <t>142,05; 854,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 70,42</t>
+          <t>-23,73; 70,31</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,72</t>
+          <t>3,33; 7,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,3</t>
+          <t>2,71; 6,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,15</t>
+          <t>3,45; 7,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83,64; 366,54</t>
+          <t>84,49; 386,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>114,9; 605,76</t>
+          <t>129,87; 641,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>113,61; 598,0</t>
+          <t>105,65; 567,98</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,2</t>
+          <t>2,81; 7,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,83</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,99</t>
+          <t>-0,77; 6,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70,56; 561,39</t>
+          <t>78,42; 581,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,71; 433,07</t>
+          <t>65,71; 383,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 275,06</t>
+          <t>-12,04; 248,89</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,12</t>
+          <t>3,09; 7,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,1</t>
+          <t>2,4; 6,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,5</t>
+          <t>1,29; 5,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,52; 362,88</t>
+          <t>83,41; 355,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,87; 393,77</t>
+          <t>86,56; 438,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,85; 155,74</t>
+          <t>24,66; 161,17</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,65</t>
+          <t>4,44; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,22 +964,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,74</t>
+          <t>2,09; 4,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149,08; 326,82</t>
+          <t>149,52; 324,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>158,33; 353,73</t>
+          <t>156,58; 344,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,83; 154,67</t>
+          <t>51,33; 159,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P14B23-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,71</t>
+          <t>4,8; 9,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,81</t>
+          <t>4,01; 8,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,12</t>
+          <t>-1,09; 3,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166,6; 743,94</t>
+          <t>160,61; 753,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>142,05; 854,33</t>
+          <t>133,32; 727,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 70,31</t>
+          <t>-15,63; 76,26</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>240,53%</t>
+          <t>188,08%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,61</t>
+          <t>3,28; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,33</t>
+          <t>2,74; 6,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,02</t>
+          <t>3,0; 6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,49; 386,35</t>
+          <t>85,45; 348,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>129,87; 641,98</t>
+          <t>124,1; 611,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>105,65; 567,98</t>
+          <t>89,26; 338,62</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>112,01%</t>
+          <t>184,58%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,47</t>
+          <t>2,86; 7,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,59</t>
+          <t>2,19; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 6,7</t>
+          <t>3,95; 8,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,42; 581,14</t>
+          <t>81,38; 608,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,71; 383,78</t>
+          <t>59,17; 446,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 248,89</t>
+          <t>82,51; 382,24</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,17</t>
+          <t>3,11; 7,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,11</t>
+          <t>2,52; 6,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,55</t>
+          <t>2,15; 5,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83,41; 355,55</t>
+          <t>80,27; 358,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,56; 438,53</t>
+          <t>89,1; 403,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,66; 161,17</t>
+          <t>39,85; 177,52</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>109,27%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,66</t>
+          <t>4,48; 6,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,73</t>
+          <t>3,79; 5,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,79</t>
+          <t>3,1; 5,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149,52; 324,38</t>
+          <t>149,19; 317,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>156,58; 344,64</t>
+          <t>164,33; 345,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,33; 159,68</t>
+          <t>69,2; 156,78</t>
         </is>
       </c>
     </row>
